--- a/plantillas/datos_mes.xlsx
+++ b/plantillas/datos_mes.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eef3e5cf01dda3ae/Documentos/informe_promociones_local/informe_promociones_local/plantillas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="11_82B14DD58DE57CF53B309B5475C2F32F27814611" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FED78CF-D9E1-4D0D-BD75-63AFA955D53F}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="11_82B14DD58DE57CF53B309B5475C2F32F27814611" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96DE9AC5-84D5-45C2-AC75-DBBEB580759D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Produccion" sheetId="1" r:id="rId1"/>
     <sheet name="Portfolio" sheetId="2" r:id="rId2"/>
     <sheet name="Captaciones" sheetId="3" r:id="rId3"/>
     <sheet name="Pte de cobro" sheetId="4" r:id="rId4"/>
+    <sheet name="Agencias" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="296">
   <si>
     <t>Mes</t>
   </si>
@@ -877,6 +878,54 @@
   <si>
     <t>Cantidad en produccion pte, €</t>
   </si>
+  <si>
+    <t>KPI</t>
+  </si>
+  <si>
+    <t>Enero</t>
+  </si>
+  <si>
+    <t>Febrero</t>
+  </si>
+  <si>
+    <t>Marzo</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>Mayo</t>
+  </si>
+  <si>
+    <t>Junio</t>
+  </si>
+  <si>
+    <t>Julio</t>
+  </si>
+  <si>
+    <t>Agosto</t>
+  </si>
+  <si>
+    <t>Septiembre</t>
+  </si>
+  <si>
+    <t>Octubre</t>
+  </si>
+  <si>
+    <t>Noviembre</t>
+  </si>
+  <si>
+    <t>Diciembre</t>
+  </si>
+  <si>
+    <t>Agencias visitadas</t>
+  </si>
+  <si>
+    <t>Leads de agencias</t>
+  </si>
+  <si>
+    <t>Comunicaciones de marketing</t>
+  </si>
 </sst>
 </file>
 
@@ -14997,7 +15046,7 @@
       <c r="Y27" s="7"/>
       <c r="Z27" s="7"/>
     </row>
-    <row r="28" spans="1:26" ht="25">
+    <row r="28" spans="1:26" ht="37.5">
       <c r="A28" s="7" t="s">
         <v>210</v>
       </c>
@@ -42626,4 +42675,130 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E42DB1F3-D9BB-40A9-90FD-EE3816229151}">
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5"/>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E1" t="s">
+        <v>284</v>
+      </c>
+      <c r="F1" t="s">
+        <v>285</v>
+      </c>
+      <c r="G1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I1" t="s">
+        <v>288</v>
+      </c>
+      <c r="J1" t="s">
+        <v>289</v>
+      </c>
+      <c r="K1" t="s">
+        <v>290</v>
+      </c>
+      <c r="L1" t="s">
+        <v>291</v>
+      </c>
+      <c r="M1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B2">
+        <v>21</v>
+      </c>
+      <c r="C2">
+        <v>18</v>
+      </c>
+      <c r="D2">
+        <v>40</v>
+      </c>
+      <c r="E2">
+        <v>22</v>
+      </c>
+      <c r="F2">
+        <v>18</v>
+      </c>
+      <c r="G2">
+        <v>23</v>
+      </c>
+      <c r="H2">
+        <v>15</v>
+      </c>
+      <c r="I2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>21</v>
+      </c>
+      <c r="G3">
+        <v>35</v>
+      </c>
+      <c r="H3">
+        <v>37</v>
+      </c>
+      <c r="I3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>17</v>
+      </c>
+      <c r="G4">
+        <v>15</v>
+      </c>
+      <c r="H4">
+        <v>21</v>
+      </c>
+      <c r="I4">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/plantillas/datos_mes.xlsx
+++ b/plantillas/datos_mes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eef3e5cf01dda3ae/Documentos/informe_promociones_local/informe_promociones_local/plantillas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="11_82B14DD58DE57CF53B309B5475C2F32F27814611" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96DE9AC5-84D5-45C2-AC75-DBBEB580759D}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="11_82B14DD58DE57CF53B309B5475C2F32F27814611" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AA4FCDE-9C8A-4B1F-AA55-6738488355A8}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Produccion" sheetId="1" r:id="rId1"/>
@@ -42559,7 +42559,7 @@
         <v>50</v>
       </c>
       <c r="C3" s="26">
-        <v>1000</v>
+        <v>14070</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -42570,7 +42570,7 @@
         <v>39</v>
       </c>
       <c r="C4" s="26">
-        <v>1000</v>
+        <v>17212</v>
       </c>
     </row>
     <row r="5" spans="1:3">

--- a/plantillas/datos_mes.xlsx
+++ b/plantillas/datos_mes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eef3e5cf01dda3ae/Documentos/informe_promociones_local/informe_promociones_local/plantillas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="11_82B14DD58DE57CF53B309B5475C2F32F27814611" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31666777-40C5-48D6-ADD1-EE51154576EF}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="11_82B14DD58DE57CF53B309B5475C2F32F27814611" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C5935D8-793B-4575-8631-84C8622CAF6E}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Produccion" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="309">
   <si>
     <t>Mes</t>
   </si>
@@ -929,13 +929,50 @@
   <si>
     <t>-</t>
   </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="mmm\-d"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$€-C0A]_-;\-* #,##0.00\ [$€-C0A]_-;_-* &quot;-&quot;??\ [$€-C0A]_-;_-@_-"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -999,7 +1036,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1059,6 +1096,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -15049,7 +15089,7 @@
       <c r="Y27" s="7"/>
       <c r="Z27" s="7"/>
     </row>
-    <row r="28" spans="1:26" ht="37.5">
+    <row r="28" spans="1:26" ht="25">
       <c r="A28" s="7" t="s">
         <v>210</v>
       </c>
@@ -42529,7 +42569,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="27.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.90625" style="26"/>
+    <col min="2" max="2" width="10.90625" style="26"/>
+    <col min="3" max="3" width="12.7265625" style="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="37.5">
@@ -42550,7 +42591,7 @@
       <c r="B2" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="27">
         <v>49050</v>
       </c>
     </row>
@@ -42559,10 +42600,10 @@
         <v>35</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>296</v>
+        <v>276</v>
+      </c>
+      <c r="C3" s="27">
+        <v>9537.81</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -42572,7 +42613,7 @@
       <c r="B4" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <v>19293.75</v>
       </c>
     </row>
@@ -42583,7 +42624,7 @@
       <c r="B5" s="25" t="s">
         <v>277</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <v>163853.20000000001</v>
       </c>
     </row>
@@ -42594,7 +42635,7 @@
       <c r="B6" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="27" t="s">
         <v>296</v>
       </c>
     </row>
@@ -42605,7 +42646,7 @@
       <c r="B7" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="27" t="s">
         <v>296</v>
       </c>
     </row>
@@ -42614,9 +42655,9 @@
         <v>56</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="26">
+        <v>39</v>
+      </c>
+      <c r="C8" s="27">
         <v>5933.88</v>
       </c>
     </row>
@@ -42627,8 +42668,8 @@
       <c r="B9" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="26" t="s">
-        <v>296</v>
+      <c r="C9" s="27">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -42636,9 +42677,9 @@
         <v>61</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="26">
+        <v>276</v>
+      </c>
+      <c r="C10" s="27">
         <v>47880</v>
       </c>
     </row>
@@ -42647,10 +42688,10 @@
         <v>63</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>276</v>
-      </c>
-      <c r="C11" s="26">
-        <v>77717.5</v>
+        <v>39</v>
+      </c>
+      <c r="C11" s="27">
+        <v>32917.5</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -42658,9 +42699,9 @@
         <v>65</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>276</v>
-      </c>
-      <c r="C12" s="26">
+        <v>39</v>
+      </c>
+      <c r="C12" s="27">
         <v>78570</v>
       </c>
     </row>
@@ -42671,7 +42712,7 @@
       <c r="B13" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="27" t="s">
         <v>296</v>
       </c>
     </row>
@@ -42736,28 +42777,30 @@
       <c r="B2" s="6">
         <v>21</v>
       </c>
-      <c r="C2" s="6">
-        <v>18</v>
+      <c r="C2" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="D2" s="6">
         <v>40</v>
       </c>
-      <c r="E2" s="6">
-        <v>22</v>
-      </c>
-      <c r="F2" s="6">
-        <v>18</v>
-      </c>
-      <c r="G2" s="6">
-        <v>23</v>
-      </c>
-      <c r="H2" s="6">
-        <v>15</v>
-      </c>
-      <c r="I2" s="6">
-        <v>13</v>
-      </c>
-      <c r="J2" s="6"/>
+      <c r="E2" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>305</v>
+      </c>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
@@ -42769,24 +42812,30 @@
       <c r="B3" s="6">
         <v>5</v>
       </c>
-      <c r="C3" s="6">
-        <v>7</v>
-      </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6">
-        <v>21</v>
-      </c>
-      <c r="G3" s="6">
-        <v>35</v>
-      </c>
-      <c r="H3" s="6">
-        <v>37</v>
-      </c>
-      <c r="I3" s="6">
-        <v>18</v>
-      </c>
-      <c r="J3" s="6"/>
+      <c r="C3" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>306</v>
+      </c>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
@@ -42795,14 +42844,18 @@
       <c r="A4" t="s">
         <v>295</v>
       </c>
-      <c r="B4" s="6"/>
+      <c r="B4" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="C4" s="6">
         <v>7</v>
       </c>
-      <c r="D4" s="6">
-        <v>5</v>
-      </c>
-      <c r="E4" s="6"/>
+      <c r="D4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>52</v>
+      </c>
       <c r="F4" s="6">
         <v>17</v>
       </c>
@@ -42815,7 +42868,9 @@
       <c r="I4" s="6">
         <v>18</v>
       </c>
-      <c r="J4" s="6"/>
+      <c r="J4" s="6" t="s">
+        <v>307</v>
+      </c>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>

--- a/plantillas/datos_mes.xlsx
+++ b/plantillas/datos_mes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eef3e5cf01dda3ae/Documentos/informe_promociones_local/informe_promociones_local/plantillas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="11_82B14DD58DE57CF53B309B5475C2F32F27814611" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C5935D8-793B-4575-8631-84C8622CAF6E}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="11_82B14DD58DE57CF53B309B5475C2F32F27814611" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15A84C64-D2C1-4F36-A456-6CDDE090753E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Produccion" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="320">
   <si>
     <t>Mes</t>
   </si>
@@ -927,9 +927,6 @@
     <t>Comunicaciones de marketing</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>49</t>
   </si>
   <si>
@@ -964,6 +961,42 @@
   </si>
   <si>
     <t>16</t>
+  </si>
+  <si>
+    <t>Solaris</t>
+  </si>
+  <si>
+    <t>Altoasis</t>
+  </si>
+  <si>
+    <t>Casares Bay</t>
+  </si>
+  <si>
+    <t>Portamare</t>
+  </si>
+  <si>
+    <t>Be Grand</t>
+  </si>
+  <si>
+    <t>Balcón del Mediterráneo</t>
+  </si>
+  <si>
+    <t>Doña Rafaela</t>
+  </si>
+  <si>
+    <t>Lake Essence</t>
+  </si>
+  <si>
+    <t>Inesia</t>
+  </si>
+  <si>
+    <t>Almendrales</t>
+  </si>
+  <si>
+    <t>MontePalatino</t>
+  </si>
+  <si>
+    <t>Arbitana</t>
   </si>
 </sst>
 </file>
@@ -15089,7 +15122,7 @@
       <c r="Y27" s="7"/>
       <c r="Z27" s="7"/>
     </row>
-    <row r="28" spans="1:26" ht="25">
+    <row r="28" spans="1:26" ht="37.5">
       <c r="A28" s="7" t="s">
         <v>210</v>
       </c>
@@ -42586,10 +42619,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="25" t="s">
-        <v>59</v>
+        <v>308</v>
+      </c>
+      <c r="B2" s="25">
+        <v>6</v>
       </c>
       <c r="C2" s="27">
         <v>49050</v>
@@ -42597,65 +42630,65 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>276</v>
+        <v>310</v>
+      </c>
+      <c r="B3" s="25">
+        <v>2</v>
       </c>
       <c r="C3" s="27">
-        <v>9537.81</v>
+        <v>47880</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>39</v>
+        <v>317</v>
+      </c>
+      <c r="B4" s="25">
+        <v>8</v>
       </c>
       <c r="C4" s="27">
-        <v>19293.75</v>
+        <v>46070.5</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>277</v>
+        <v>309</v>
+      </c>
+      <c r="B5" s="25">
+        <v>1</v>
       </c>
       <c r="C5" s="27">
-        <v>163853.20000000001</v>
+        <v>32917.5</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>296</v>
+        <v>316</v>
+      </c>
+      <c r="B6" s="25">
+        <v>2</v>
+      </c>
+      <c r="C6" s="27">
+        <v>19293.75</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>296</v>
+        <v>319</v>
+      </c>
+      <c r="B7" s="25">
+        <v>2</v>
+      </c>
+      <c r="C7" s="27">
+        <v>9537.8100000000013</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>39</v>
+        <v>314</v>
+      </c>
+      <c r="B8" s="25">
+        <v>1</v>
       </c>
       <c r="C8" s="27">
         <v>5933.88</v>
@@ -42663,10 +42696,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>34</v>
+        <v>311</v>
+      </c>
+      <c r="B9" s="25">
+        <v>0</v>
       </c>
       <c r="C9" s="27">
         <v>0</v>
@@ -42674,49 +42707,52 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>276</v>
+        <v>312</v>
+      </c>
+      <c r="B10" s="25">
+        <v>0</v>
       </c>
       <c r="C10" s="27">
-        <v>47880</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>39</v>
+        <v>313</v>
+      </c>
+      <c r="B11" s="25">
+        <v>0</v>
       </c>
       <c r="C11" s="27">
-        <v>32917.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>39</v>
+        <v>315</v>
+      </c>
+      <c r="B12" s="25">
+        <v>0</v>
       </c>
       <c r="C12" s="27">
-        <v>78570</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>296</v>
+        <v>318</v>
+      </c>
+      <c r="B13" s="25">
+        <v>0</v>
+      </c>
+      <c r="C13" s="27">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C13">
+    <sortCondition descending="1" ref="C2:C13"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -42784,22 +42820,22 @@
         <v>40</v>
       </c>
       <c r="E2" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>298</v>
-      </c>
       <c r="G2" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
@@ -42816,25 +42852,25 @@
         <v>57</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>68</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
@@ -42869,7 +42905,7 @@
         <v>18</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
